--- a/data/trans_orig/IP24_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69793</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84576</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>76652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92958</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149537</t>
+          <t>150690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172107</t>
+          <t>172855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27070</t>
+          <t>27885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43563</t>
+          <t>43376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>53345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76663</t>
+          <t>75510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41821</t>
+          <t>40898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>44269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65144</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91041</t>
+          <t>91747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119990</t>
+          <t>120196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188800</t>
+          <t>189423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209930</t>
+          <t>210853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188612</t>
+          <t>189403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209593</t>
+          <t>209487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385517</t>
+          <t>385311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>414466</t>
+          <t>413760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104760</t>
+          <t>104741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116271</t>
+          <t>116642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121577</t>
+          <t>121477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132529</t>
+          <t>132762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230669</t>
+          <t>230361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246376</t>
+          <t>245673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>33518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54357</t>
+          <t>54064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157448</t>
+          <t>157967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173926</t>
+          <t>173502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184143</t>
+          <t>182742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195906</t>
+          <t>195561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345789</t>
+          <t>346082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365919</t>
+          <t>366628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151063</t>
+          <t>150375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188270</t>
+          <t>187450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>313924</t>
+          <t>314300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366474</t>
+          <t>366319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489127</t>
+          <t>488982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525438</t>
+          <t>524416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>533078</t>
+          <t>533898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>570285</t>
+          <t>570973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033809</t>
+          <t>1033964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1086359</t>
+          <t>1085983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75688</t>
+          <t>74920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93683</t>
+          <t>93752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>81772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99085</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>161292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188156</t>
+          <t>188485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50145</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68140</t>
+          <t>68908</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40032</t>
+          <t>38596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58245</t>
+          <t>57345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94789</t>
+          <t>94460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121414</t>
+          <t>121653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195641</t>
+          <t>196760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213660</t>
+          <t>213600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243740</t>
+          <t>242827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256469</t>
+          <t>256406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446448</t>
+          <t>445372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>467457</t>
+          <t>467415</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145114</t>
+          <t>144742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153304</t>
+          <t>153160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151509</t>
+          <t>152173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298613</t>
+          <t>299485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308686</t>
+          <t>308600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>18106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>33809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25109</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43184</t>
+          <t>45861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139008</t>
+          <t>137528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153458</t>
+          <t>153231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164086</t>
+          <t>163775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174310</t>
+          <t>174733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308108</t>
+          <t>305431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326183</t>
+          <t>324910</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101268</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134647</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238919</t>
+          <t>237913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>285448</t>
+          <t>284186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544603</t>
+          <t>545706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>579403</t>
+          <t>579707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>608309</t>
+          <t>606500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641688</t>
+          <t>641575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1163246</t>
+          <t>1164508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209775</t>
+          <t>1210781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72995</t>
+          <t>73770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90350</t>
+          <t>91475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62266</t>
+          <t>62682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79596</t>
+          <t>79517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141054</t>
+          <t>142340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165689</t>
+          <t>165739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40634</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57989</t>
+          <t>57214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42023</t>
+          <t>42102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59353</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86914</t>
+          <t>86864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111549</t>
+          <t>110263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,65%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41704</t>
+          <t>41074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26482</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43309</t>
+          <t>43165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54896</t>
+          <t>55774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79501</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168813</t>
+          <t>169443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185846</t>
+          <t>186306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214752</t>
+          <t>214896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231579</t>
+          <t>232558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389077</t>
+          <t>388504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413682</t>
+          <t>412804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>30911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166796</t>
+          <t>166254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>179186</t>
+          <t>179013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174924</t>
+          <t>174986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183501</t>
+          <t>183675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344974</t>
+          <t>345513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360819</t>
+          <t>360398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46112</t>
+          <t>46537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139692</t>
+          <t>140435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154798</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156533</t>
+          <t>156219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166931</t>
+          <t>167725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299850</t>
+          <t>299425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319338</t>
+          <t>318986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>139898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>531236</t>
+          <t>530298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>566260</t>
+          <t>566322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>598222</t>
+          <t>600655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>630737</t>
+          <t>632549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1139444</t>
+          <t>1141063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1187687</t>
+          <t>1188058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48178</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64207</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36315</t>
+          <t>36536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50364</t>
+          <t>49991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66393</t>
+          <t>66142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>38030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>50409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114855</t>
+          <t>114279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133868</t>
+          <t>133836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144558</t>
+          <t>144060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160874</t>
+          <t>160565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>263520</t>
+          <t>265463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>289429</t>
+          <t>290980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20356</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38503</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60905</t>
+          <t>63543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143641</t>
+          <t>143743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158713</t>
+          <t>158712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172164</t>
+          <t>172303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191197</t>
+          <t>192093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>323720</t>
+          <t>321082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346122</t>
+          <t>346034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48084</t>
+          <t>47751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130892</t>
+          <t>135168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33201</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82439</t>
+          <t>79700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>90361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209379</t>
+          <t>200561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144566</t>
+          <t>140290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227374</t>
+          <t>227707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223044</t>
+          <t>225783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272282</t>
+          <t>271663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>371561</t>
+          <t>380379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>491716</t>
+          <t>490579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125608</t>
+          <t>124635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>115769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252371</t>
+          <t>251372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>368345</t>
+          <t>362673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425963</t>
+          <t>434516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538221</t>
+          <t>539194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>588444</t>
+          <t>589268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641684</t>
+          <t>641928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1053181</t>
+          <t>1058853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1169155</t>
+          <t>1170154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>85074</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>76550</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92782</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>77305</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>69378</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83945</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>69914</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>84192</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>72,81%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>85074</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>76652</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>92143</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150690</t>
+          <t>151039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172855</t>
+          <t>172449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34954</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27246</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43478</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28866</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22226</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36793</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21979</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36257</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34954</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27885</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>43376</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53345</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75510</t>
+          <t>75161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>120028</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>120028</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120028</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>120028</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>120028</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>120028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54371</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44548</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>65745</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>51694</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>40898</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62328</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42207</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62996</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>44269</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>64353</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91747</t>
+          <t>91643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120196</t>
+          <t>121911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>199385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>188011</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>209208</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>200057</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>189423</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>210853</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>188755</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>209544</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>199385</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>189403</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>209487</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385311</t>
+          <t>383596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413760</t>
+          <t>413864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>251751</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>251751</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>251751</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13705</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9147</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19926</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15600</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10274</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22175</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10093</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21865</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>29306</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>21747</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>38408</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>8,1%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13705</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8753</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20038</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>29306</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>22757</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>38069</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -1522,107 +1522,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>127810</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121589</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132368</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>111316</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>104741</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>116642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>105051</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>116823</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,77%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>239124</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>230022</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>246683</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>85,69%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>91,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>127810</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121477</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132762</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,32%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>93,82%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>239124</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>230361</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>245673</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>89,08%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>85,82%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>126916</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>126916</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>126916</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15722</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10314</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22502</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>27131</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20595</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19706</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35184</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15722</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10488</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23307</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33518</t>
+          <t>33933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54064</t>
+          <t>53704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>190327</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>183547</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>195735</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>166966</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157967</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>173502</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158913</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>174391</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>190327</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>182742</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>195561</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346082</t>
+          <t>346442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366628</t>
+          <t>366213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>151269</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>187574</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>171730</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>154519</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>189953</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>154794</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>190240</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>168873</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>150375</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>187450</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314300</t>
+          <t>313929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366319</t>
+          <t>365840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>552475</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>533774</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>570079</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>755</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>507205</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>488982</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>524416</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>488695</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>524141</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>74,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>72,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>552475</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>533898</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>570973</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033964</t>
+          <t>1034443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1085983</t>
+          <t>1086354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>721348</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>721348</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>721348</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>678935</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>678935</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>678935</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>721348</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>721348</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>721348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90579</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81120</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>99787</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>84118</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>74920</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>93752</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>93655</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>58,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>90579</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>81772</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>100521</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161292</t>
+          <t>160407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188485</t>
+          <t>186443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48538</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39330</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57997</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59710</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50076</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>68908</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50173</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70144</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>41,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>48538</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38596</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>57345</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94460</t>
+          <t>96502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121653</t>
+          <t>122538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>139117</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>139117</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>139117</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>143828</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>143828</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>143828</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139117</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>139117</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>139117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16172</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10582</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23633</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>28105</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20567</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37407</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19985</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>37735</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16172</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10557</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24136</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33715</t>
+          <t>34414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55758</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>250791</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>243330</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>256381</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>206062</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>196760</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>213600</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>196432</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>214182</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250791</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>242827</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>256406</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>445372</t>
+          <t>445993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>467415</t>
+          <t>466716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>266963</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>266963</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>266963</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234167</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234167</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234167</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>266963</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>266963</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>266963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5295</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6523</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3246</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11664</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11606</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154944</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>151626</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156287</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>149883</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>144742</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>153160</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>144800</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153156</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>97,92%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154944</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>152173</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156289</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>435</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299485</t>
+          <t>299510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308600</t>
+          <t>308725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156921</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156921</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156921</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156406</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156406</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156406</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156921</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156921</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15958</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24705</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18106</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33809</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18118</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33137</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>14,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>10,57%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9718</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5222</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16180</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170237</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163997</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174502</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>146632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>137528</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153231</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>138200</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>153219</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>85,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>80,66%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>89,43%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>170237</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>163775</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174733</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,6%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>458</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305431</t>
+          <t>306343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324910</t>
+          <t>325221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>102726</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>136006</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>143451</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>126031</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>160032</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>127592</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>161534</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>118446</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>101381</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>136456</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237913</t>
+          <t>235037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284186</t>
+          <t>285202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>624510</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>606950</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>640230</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>562287</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>545706</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>579707</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>544204</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>578146</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>624510</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>606500</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>641575</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1164508</t>
+          <t>1163492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1210781</t>
+          <t>1213657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>742956</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>742956</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>742956</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>705738</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>705738</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>705738</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>742956</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>742956</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>742956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62699</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>79920</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>82542</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>73770</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91475</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>73921</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>90850</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>71321</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>62682</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>79517</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>58,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142340</t>
+          <t>140459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>165983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50298</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41699</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>58920</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48442</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39509</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57214</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40134</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57063</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50298</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>42102</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58937</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>41,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86864</t>
+          <t>86620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110263</t>
+          <t>112144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121619</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121619</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121619</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130984</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130984</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130984</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121619</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121619</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121619</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34611</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25725</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>42797</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>32373</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24211</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41074</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24885</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>40806</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>15,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>34611</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>25503</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>43165</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55774</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80074</t>
+          <t>79213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>223450</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>215264</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>232336</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>178144</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>169443</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>186306</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>169711</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>185632</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>223450</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>214896</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>232558</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,59%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>388504</t>
+          <t>389365</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>412804</t>
+          <t>413946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4155</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12973</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15035</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9886</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22645</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21656</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7498</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12539</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30911</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -5421,67 +5421,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>180027</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>174552</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>183370</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>173864</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>166254</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>179013</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>167243</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>179539</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>180027</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>174986</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>183675</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345513</t>
+          <t>345179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360398</t>
+          <t>360623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187525</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187525</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187525</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187525</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187525</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10975</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17430</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24415</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17291</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32179</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17016</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33084</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>14,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10975</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5623</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17129</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46537</t>
+          <t>45487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>162373</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>155918</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167251</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>148199</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140435</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>155323</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>139530</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>155598</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>85,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>162373</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>156219</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>167725</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299425</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318986</t>
+          <t>318976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173348</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173348</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173348</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172614</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172614</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172614</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173348</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173348</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173348</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>107953</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140703</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>154366</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>136692</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>172716</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>137167</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>171263</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,96%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>124404</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>108004</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>139898</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255509</t>
+          <t>254577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302504</t>
+          <t>303220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>616149</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>599850</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>632600</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>822</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>548648</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>530298</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>566322</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>531751</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>565847</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>78,04%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>80,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>616149</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>600655</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>632549</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1141063</t>
+          <t>1140347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1188058</t>
+          <t>1188990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -6220,52 +6220,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>703014</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703014</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703014</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25257</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20547</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29963</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25352</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19464</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30929</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56032</t>
+          <t>46657</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>54249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18294</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27710</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30648</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25071</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36536</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21861</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33787</t>
+          <t>33935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58539</t>
+          <t>52379</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49991</t>
+          <t>44787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>58798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23667</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17407</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31069</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33644</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25463</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45020</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,12%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21525</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>49644</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50409</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75926</t>
+          <t>59552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>133496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>126094</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>139756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>125655</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>114279</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133836</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>153178</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144060</t>
+          <t>112554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160565</t>
+          <t>126162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>278833</t>
+          <t>253037</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265463</t>
+          <t>243129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290980</t>
+          <t>263031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24420</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16911</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33569</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20884</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14360</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29329</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39250</t>
+          <t>30962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49333</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>57936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>174743</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>165594</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>182252</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>152188</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143743</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158712</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>183104</t>
+          <t>153218</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172303</t>
+          <t>143710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>192093</t>
+          <t>160003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>335292</t>
+          <t>327961</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321082</t>
+          <t>315899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346034</t>
+          <t>338682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29698</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65907</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>75515</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47751</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>135168</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47461</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122976</t>
+          <t>85255</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>69574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200561</t>
+          <t>114060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>250645</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>226738</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>262947</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>199943</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140290</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>227707</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>72,59%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>258022</t>
+          <t>213299</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225783</t>
+          <t>200202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271663</t>
+          <t>222793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>457964</t>
+          <t>463943</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380379</t>
+          <t>435138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490579</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144738</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>124635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>229313</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>128550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251372</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362673</t>
+          <t>256861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>581884</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>552490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>598322</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>508434</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>434516</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>539194</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>622196</t>
+          <t>515435</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>498972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641928</t>
+          <t>530485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1130630</t>
+          <t>1097319</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058853</t>
+          <t>1067889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1170154</t>
+          <t>1120398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
